--- a/data/metadata_raw/retail_trade.xlsx
+++ b/data/metadata_raw/retail_trade.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1240">
   <si>
     <t>Code</t>
   </si>
@@ -2852,6 +2852,9 @@
     <t>Бухоро тумани</t>
   </si>
   <si>
+    <t>Вобкент тумани</t>
+  </si>
+  <si>
     <t>Ғиждувон тумани</t>
   </si>
   <si>
@@ -3608,7 +3611,7 @@
     <t>2023-05-10</t>
   </si>
   <si>
-    <t>2024-08-23</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>1.07.02.0001</t>
@@ -6723,7 +6726,7 @@
         <v>724</v>
       </c>
       <c r="E43" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F43">
         <v>80</v>
@@ -6785,7 +6788,7 @@
         <v>725</v>
       </c>
       <c r="E44" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F44">
         <v>211.5</v>
@@ -6847,7 +6850,7 @@
         <v>726</v>
       </c>
       <c r="E45" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F45">
         <v>17.7</v>
@@ -6909,7 +6912,7 @@
         <v>727</v>
       </c>
       <c r="E46" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F46">
         <v>67.59999999999999</v>
@@ -6971,7 +6974,7 @@
         <v>728</v>
       </c>
       <c r="E47" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F47">
         <v>15.8</v>
@@ -7033,7 +7036,7 @@
         <v>729</v>
       </c>
       <c r="E48" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F48">
         <v>32.1</v>
@@ -7095,7 +7098,7 @@
         <v>730</v>
       </c>
       <c r="E49" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F49">
         <v>71.09999999999999</v>
@@ -7157,7 +7160,7 @@
         <v>731</v>
       </c>
       <c r="E50" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -7219,7 +7222,7 @@
         <v>732</v>
       </c>
       <c r="E51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F51">
         <v>53.5</v>
@@ -7281,7 +7284,7 @@
         <v>733</v>
       </c>
       <c r="E52" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F52">
         <v>629.6</v>
@@ -7343,7 +7346,7 @@
         <v>734</v>
       </c>
       <c r="E53" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F53">
         <v>203.5</v>
@@ -7405,7 +7408,7 @@
         <v>735</v>
       </c>
       <c r="E54" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F54">
         <v>14.2</v>
@@ -7467,7 +7470,7 @@
         <v>736</v>
       </c>
       <c r="E55" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F55">
         <v>66</v>
@@ -7529,7 +7532,7 @@
         <v>737</v>
       </c>
       <c r="E56" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F56">
         <v>66.2</v>
@@ -7591,7 +7594,7 @@
         <v>738</v>
       </c>
       <c r="E57" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F57">
         <v>47</v>
@@ -7653,7 +7656,7 @@
         <v>739</v>
       </c>
       <c r="E58" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F58">
         <v>34.9</v>
@@ -7715,7 +7718,7 @@
         <v>740</v>
       </c>
       <c r="E59" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F59">
         <v>78.3</v>
@@ -7777,7 +7780,7 @@
         <v>741</v>
       </c>
       <c r="E60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F60">
         <v>24</v>
@@ -7839,7 +7842,7 @@
         <v>742</v>
       </c>
       <c r="E61" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F61">
         <v>18.4</v>
@@ -7901,7 +7904,7 @@
         <v>743</v>
       </c>
       <c r="E62" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F62">
         <v>3.6</v>
@@ -7963,7 +7966,7 @@
         <v>744</v>
       </c>
       <c r="E63" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F63">
         <v>31.7</v>
@@ -8025,7 +8028,7 @@
         <v>745</v>
       </c>
       <c r="E64" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F64">
         <v>31</v>
@@ -8087,7 +8090,7 @@
         <v>746</v>
       </c>
       <c r="E65" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F65">
         <v>10.8</v>
@@ -8149,7 +8152,7 @@
         <v>747</v>
       </c>
       <c r="E66" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F66">
         <v>1325.2</v>
@@ -8211,7 +8214,7 @@
         <v>748</v>
       </c>
       <c r="E67" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F67">
         <v>552.2</v>
@@ -8273,7 +8276,7 @@
         <v>749</v>
       </c>
       <c r="E68" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8335,7 +8338,7 @@
         <v>750</v>
       </c>
       <c r="E69" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8397,7 +8400,7 @@
         <v>751</v>
       </c>
       <c r="E70" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F70">
         <v>52.7</v>
@@ -8459,7 +8462,7 @@
         <v>752</v>
       </c>
       <c r="E71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F71">
         <v>37.7</v>
@@ -8521,7 +8524,7 @@
         <v>753</v>
       </c>
       <c r="E72" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F72">
         <v>76.8</v>
@@ -8583,7 +8586,7 @@
         <v>754</v>
       </c>
       <c r="E73" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F73">
         <v>41</v>
@@ -8645,7 +8648,7 @@
         <v>755</v>
       </c>
       <c r="E74" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F74">
         <v>98.2</v>
@@ -8707,7 +8710,7 @@
         <v>756</v>
       </c>
       <c r="E75" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F75">
         <v>95.40000000000001</v>
@@ -8769,7 +8772,7 @@
         <v>757</v>
       </c>
       <c r="E76" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F76">
         <v>26.4</v>
@@ -8831,7 +8834,7 @@
         <v>758</v>
       </c>
       <c r="E77" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F77">
         <v>28.6</v>
@@ -8893,7 +8896,7 @@
         <v>759</v>
       </c>
       <c r="E78" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F78">
         <v>43.3</v>
@@ -8955,7 +8958,7 @@
         <v>760</v>
       </c>
       <c r="E79" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F79">
         <v>23.2</v>
@@ -9017,7 +9020,7 @@
         <v>761</v>
       </c>
       <c r="E80" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F80">
         <v>57.2</v>
@@ -9079,7 +9082,7 @@
         <v>762</v>
       </c>
       <c r="E81" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F81">
         <v>111.3</v>
@@ -9141,7 +9144,7 @@
         <v>763</v>
       </c>
       <c r="E82" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F82">
         <v>81.09999999999999</v>
@@ -9203,7 +9206,7 @@
         <v>764</v>
       </c>
       <c r="E83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F83">
         <v>850.6</v>
@@ -9265,7 +9268,7 @@
         <v>765</v>
       </c>
       <c r="E84" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F84">
         <v>326.1</v>
@@ -9327,7 +9330,7 @@
         <v>766</v>
       </c>
       <c r="E85" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F85">
         <v>107.6</v>
@@ -9389,7 +9392,7 @@
         <v>767</v>
       </c>
       <c r="E86" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9451,7 +9454,7 @@
         <v>768</v>
       </c>
       <c r="E87" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F87">
         <v>23.4</v>
@@ -9513,7 +9516,7 @@
         <v>769</v>
       </c>
       <c r="E88" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F88">
         <v>73.5</v>
@@ -9575,7 +9578,7 @@
         <v>770</v>
       </c>
       <c r="E89" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F89">
         <v>22.6</v>
@@ -9637,7 +9640,7 @@
         <v>771</v>
       </c>
       <c r="E90" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F90">
         <v>122.8</v>
@@ -9699,7 +9702,7 @@
         <v>772</v>
       </c>
       <c r="E91" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F91">
         <v>31</v>
@@ -9761,7 +9764,7 @@
         <v>773</v>
       </c>
       <c r="E92" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F92">
         <v>18</v>
@@ -9823,7 +9826,7 @@
         <v>774</v>
       </c>
       <c r="E93" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F93">
         <v>38.9</v>
@@ -9885,7 +9888,7 @@
         <v>775</v>
       </c>
       <c r="E94" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F94">
         <v>86.8</v>
@@ -9947,7 +9950,7 @@
         <v>776</v>
       </c>
       <c r="E95" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F95">
         <v>1297</v>
@@ -10009,7 +10012,7 @@
         <v>777</v>
       </c>
       <c r="E96" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F96">
         <v>518.3</v>
@@ -10071,7 +10074,7 @@
         <v>778</v>
       </c>
       <c r="E97" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F97">
         <v>44.3</v>
@@ -10133,7 +10136,7 @@
         <v>779</v>
       </c>
       <c r="E98" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F98">
         <v>52.6</v>
@@ -10195,7 +10198,7 @@
         <v>780</v>
       </c>
       <c r="E99" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F99">
         <v>47.2</v>
@@ -10257,7 +10260,7 @@
         <v>781</v>
       </c>
       <c r="E100" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F100">
         <v>41.5</v>
@@ -10319,7 +10322,7 @@
         <v>782</v>
       </c>
       <c r="E101" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F101">
         <v>87.59999999999999</v>
@@ -10381,7 +10384,7 @@
         <v>783</v>
       </c>
       <c r="E102" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F102">
         <v>100.2</v>
@@ -10443,7 +10446,7 @@
         <v>784</v>
       </c>
       <c r="E103" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F103">
         <v>82.2</v>
@@ -10505,7 +10508,7 @@
         <v>785</v>
       </c>
       <c r="E104" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F104">
         <v>66</v>
@@ -10567,7 +10570,7 @@
         <v>786</v>
       </c>
       <c r="E105" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F105">
         <v>44</v>
@@ -10629,7 +10632,7 @@
         <v>787</v>
       </c>
       <c r="E106" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F106">
         <v>161.5</v>
@@ -10691,7 +10694,7 @@
         <v>788</v>
       </c>
       <c r="E107" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F107">
         <v>51.6</v>
@@ -10753,7 +10756,7 @@
         <v>789</v>
       </c>
       <c r="E108" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F108">
         <v>1683</v>
@@ -10815,7 +10818,7 @@
         <v>790</v>
       </c>
       <c r="E109" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F109">
         <v>655.7</v>
@@ -10877,7 +10880,7 @@
         <v>791</v>
       </c>
       <c r="E110" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F110">
         <v>87.7</v>
@@ -10939,7 +10942,7 @@
         <v>792</v>
       </c>
       <c r="E111" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F111">
         <v>53.7</v>
@@ -11001,7 +11004,7 @@
         <v>793</v>
       </c>
       <c r="E112" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F112">
         <v>62.8</v>
@@ -11063,7 +11066,7 @@
         <v>794</v>
       </c>
       <c r="E113" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F113">
         <v>46.6</v>
@@ -11125,7 +11128,7 @@
         <v>795</v>
       </c>
       <c r="E114" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F114">
         <v>60.5</v>
@@ -11187,7 +11190,7 @@
         <v>796</v>
       </c>
       <c r="E115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F115">
         <v>54.8</v>
@@ -11249,7 +11252,7 @@
         <v>797</v>
       </c>
       <c r="E116" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F116">
         <v>34</v>
@@ -11311,7 +11314,7 @@
         <v>798</v>
       </c>
       <c r="E117" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F117">
         <v>60.4</v>
@@ -11373,7 +11376,7 @@
         <v>799</v>
       </c>
       <c r="E118" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F118">
         <v>78.3</v>
@@ -11435,7 +11438,7 @@
         <v>800</v>
       </c>
       <c r="E119" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F119">
         <v>83.7</v>
@@ -11497,7 +11500,7 @@
         <v>801</v>
       </c>
       <c r="E120" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F120">
         <v>54.6</v>
@@ -11559,7 +11562,7 @@
         <v>802</v>
       </c>
       <c r="E121" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F121">
         <v>110.1</v>
@@ -11621,7 +11624,7 @@
         <v>803</v>
       </c>
       <c r="E122" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F122">
         <v>28.6</v>
@@ -11683,7 +11686,7 @@
         <v>804</v>
       </c>
       <c r="E123" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F123">
         <v>165.5</v>
@@ -11745,7 +11748,7 @@
         <v>805</v>
       </c>
       <c r="E124" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F124">
         <v>46</v>
@@ -11807,7 +11810,7 @@
         <v>806</v>
       </c>
       <c r="E125" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F125">
         <v>1321.3</v>
@@ -11869,7 +11872,7 @@
         <v>807</v>
       </c>
       <c r="E126" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F126">
         <v>250.6</v>
@@ -11931,7 +11934,7 @@
         <v>808</v>
       </c>
       <c r="E127" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F127">
         <v>56.2</v>
@@ -11993,7 +11996,7 @@
         <v>809</v>
       </c>
       <c r="E128" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F128">
         <v>59.4</v>
@@ -12055,7 +12058,7 @@
         <v>810</v>
       </c>
       <c r="E129" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F129">
         <v>6.9</v>
@@ -12117,7 +12120,7 @@
         <v>811</v>
       </c>
       <c r="E130" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F130">
         <v>64.09999999999999</v>
@@ -12179,7 +12182,7 @@
         <v>812</v>
       </c>
       <c r="E131" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F131">
         <v>50.1</v>
@@ -12241,7 +12244,7 @@
         <v>813</v>
       </c>
       <c r="E132" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F132">
         <v>318.4</v>
@@ -12303,7 +12306,7 @@
         <v>814</v>
       </c>
       <c r="E133" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F133">
         <v>80.40000000000001</v>
@@ -12365,7 +12368,7 @@
         <v>815</v>
       </c>
       <c r="E134" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F134">
         <v>66.8</v>
@@ -12427,7 +12430,7 @@
         <v>816</v>
       </c>
       <c r="E135" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F135">
         <v>52.2</v>
@@ -12489,7 +12492,7 @@
         <v>817</v>
       </c>
       <c r="E136" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F136">
         <v>62.1</v>
@@ -12551,7 +12554,7 @@
         <v>818</v>
       </c>
       <c r="E137" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F137">
         <v>24.5</v>
@@ -12613,7 +12616,7 @@
         <v>819</v>
       </c>
       <c r="E138" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F138">
         <v>52</v>
@@ -12675,7 +12678,7 @@
         <v>820</v>
       </c>
       <c r="E139" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F139">
         <v>78</v>
@@ -12737,7 +12740,7 @@
         <v>821</v>
       </c>
       <c r="E140" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F140">
         <v>99.59999999999999</v>
@@ -12799,7 +12802,7 @@
         <v>822</v>
       </c>
       <c r="E141" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F141">
         <v>411.1</v>
@@ -12861,7 +12864,7 @@
         <v>823</v>
       </c>
       <c r="E142" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F142">
         <v>145.6</v>
@@ -12923,7 +12926,7 @@
         <v>824</v>
       </c>
       <c r="E143" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F143">
         <v>9.699999999999999</v>
@@ -12985,7 +12988,7 @@
         <v>825</v>
       </c>
       <c r="E144" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F144">
         <v>39.5</v>
@@ -13047,7 +13050,7 @@
         <v>826</v>
       </c>
       <c r="E145" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F145">
         <v>13.9</v>
@@ -13109,7 +13112,7 @@
         <v>827</v>
       </c>
       <c r="E146" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F146">
         <v>26.5</v>
@@ -13171,7 +13174,7 @@
         <v>828</v>
       </c>
       <c r="E147" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F147">
         <v>11.7</v>
@@ -13233,7 +13236,7 @@
         <v>829</v>
       </c>
       <c r="E148" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F148">
         <v>17.5</v>
@@ -13295,7 +13298,7 @@
         <v>830</v>
       </c>
       <c r="E149" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F149">
         <v>18.4</v>
@@ -13357,7 +13360,7 @@
         <v>831</v>
       </c>
       <c r="E150" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F150">
         <v>22</v>
@@ -13419,7 +13422,7 @@
         <v>832</v>
       </c>
       <c r="E151" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F151">
         <v>87.7</v>
@@ -13481,7 +13484,7 @@
         <v>833</v>
       </c>
       <c r="E152" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F152">
         <v>18.6</v>
@@ -13543,7 +13546,7 @@
         <v>834</v>
       </c>
       <c r="E153" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F153">
         <v>2306.3</v>
@@ -13605,7 +13608,7 @@
         <v>835</v>
       </c>
       <c r="E154" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -13667,7 +13670,7 @@
         <v>836</v>
       </c>
       <c r="E155" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F155">
         <v>156.1</v>
@@ -13729,7 +13732,7 @@
         <v>837</v>
       </c>
       <c r="E156" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F156">
         <v>113.7</v>
@@ -13791,7 +13794,7 @@
         <v>838</v>
       </c>
       <c r="E157" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F157">
         <v>123</v>
@@ -13853,7 +13856,7 @@
         <v>839</v>
       </c>
       <c r="E158" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F158">
         <v>121.1</v>
@@ -13915,7 +13918,7 @@
         <v>840</v>
       </c>
       <c r="E159" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F159">
         <v>77.5</v>
@@ -13977,7 +13980,7 @@
         <v>841</v>
       </c>
       <c r="E160" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F160">
         <v>142.8</v>
@@ -14039,7 +14042,7 @@
         <v>842</v>
       </c>
       <c r="E161" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F161">
         <v>56.7</v>
@@ -14101,7 +14104,7 @@
         <v>843</v>
       </c>
       <c r="E162" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F162">
         <v>85.09999999999999</v>
@@ -14163,7 +14166,7 @@
         <v>844</v>
       </c>
       <c r="E163" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F163">
         <v>55</v>
@@ -14225,7 +14228,7 @@
         <v>845</v>
       </c>
       <c r="E164" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F164">
         <v>101.6</v>
@@ -14287,7 +14290,7 @@
         <v>846</v>
       </c>
       <c r="E165" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F165">
         <v>71.40000000000001</v>
@@ -14349,7 +14352,7 @@
         <v>847</v>
       </c>
       <c r="E166" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F166">
         <v>56.4</v>
@@ -14411,7 +14414,7 @@
         <v>848</v>
       </c>
       <c r="E167" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F167">
         <v>447.3</v>
@@ -14473,7 +14476,7 @@
         <v>849</v>
       </c>
       <c r="E168" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F168">
         <v>41.7</v>
@@ -14535,7 +14538,7 @@
         <v>850</v>
       </c>
       <c r="E169" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F169">
         <v>105.6</v>
@@ -14597,7 +14600,7 @@
         <v>851</v>
       </c>
       <c r="E170" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F170">
         <v>96.90000000000001</v>
@@ -14659,7 +14662,7 @@
         <v>852</v>
       </c>
       <c r="E171" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F171">
         <v>39.1</v>
@@ -14721,7 +14724,7 @@
         <v>853</v>
       </c>
       <c r="E172" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F172">
         <v>65</v>
@@ -14783,7 +14786,7 @@
         <v>854</v>
       </c>
       <c r="E173" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F173">
         <v>52.6</v>
@@ -14845,7 +14848,7 @@
         <v>855</v>
       </c>
       <c r="E174" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F174">
         <v>230.8</v>
@@ -14907,7 +14910,7 @@
         <v>856</v>
       </c>
       <c r="E175" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -14969,7 +14972,7 @@
         <v>857</v>
       </c>
       <c r="E176" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F176">
         <v>1911.6</v>
@@ -15031,7 +15034,7 @@
         <v>858</v>
       </c>
       <c r="E177" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F177">
         <v>441</v>
@@ -15093,7 +15096,7 @@
         <v>859</v>
       </c>
       <c r="E178" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F178">
         <v>321.1</v>
@@ -15155,7 +15158,7 @@
         <v>860</v>
       </c>
       <c r="E179" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F179">
         <v>39.5</v>
@@ -15217,7 +15220,7 @@
         <v>861</v>
       </c>
       <c r="E180" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F180">
         <v>176.5</v>
@@ -15279,7 +15282,7 @@
         <v>862</v>
       </c>
       <c r="E181" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F181">
         <v>85.59999999999999</v>
@@ -15341,7 +15344,7 @@
         <v>863</v>
       </c>
       <c r="E182" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F182">
         <v>61.9</v>
@@ -15403,7 +15406,7 @@
         <v>864</v>
       </c>
       <c r="E183" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F183">
         <v>80.09999999999999</v>
@@ -15465,7 +15468,7 @@
         <v>865</v>
       </c>
       <c r="E184" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F184">
         <v>76.8</v>
@@ -15527,7 +15530,7 @@
         <v>866</v>
       </c>
       <c r="E185" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F185">
         <v>64</v>
@@ -15589,7 +15592,7 @@
         <v>867</v>
       </c>
       <c r="E186" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F186">
         <v>47.6</v>
@@ -15651,7 +15654,7 @@
         <v>868</v>
       </c>
       <c r="E187" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F187">
         <v>57.1</v>
@@ -15713,7 +15716,7 @@
         <v>869</v>
       </c>
       <c r="E188" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F188">
         <v>30.5</v>
@@ -15775,7 +15778,7 @@
         <v>870</v>
       </c>
       <c r="E189" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F189">
         <v>55.2</v>
@@ -15837,7 +15840,7 @@
         <v>871</v>
       </c>
       <c r="E190" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F190">
         <v>49.1</v>
@@ -15899,7 +15902,7 @@
         <v>872</v>
       </c>
       <c r="E191" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F191">
         <v>112.1</v>
@@ -15961,7 +15964,7 @@
         <v>873</v>
       </c>
       <c r="E192" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F192">
         <v>43.7</v>
@@ -16023,7 +16026,7 @@
         <v>874</v>
       </c>
       <c r="E193" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F193">
         <v>37.6</v>
@@ -16085,7 +16088,7 @@
         <v>875</v>
       </c>
       <c r="E194" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F194">
         <v>88.40000000000001</v>
@@ -16147,7 +16150,7 @@
         <v>876</v>
       </c>
       <c r="E195" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F195">
         <v>43.8</v>
@@ -16209,7 +16212,7 @@
         <v>877</v>
       </c>
       <c r="E196" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F196">
         <v>1005.9</v>
@@ -16271,7 +16274,7 @@
         <v>878</v>
       </c>
       <c r="E197" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F197">
         <v>432.2</v>
@@ -16333,7 +16336,7 @@
         <v>879</v>
       </c>
       <c r="E198" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -16395,7 +16398,7 @@
         <v>880</v>
       </c>
       <c r="E199" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F199">
         <v>52.6</v>
@@ -16457,7 +16460,7 @@
         <v>881</v>
       </c>
       <c r="E200" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F200">
         <v>54.6</v>
@@ -16519,7 +16522,7 @@
         <v>882</v>
       </c>
       <c r="E201" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F201">
         <v>40.3</v>
@@ -16581,7 +16584,7 @@
         <v>883</v>
       </c>
       <c r="E202" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F202">
         <v>78.90000000000001</v>
@@ -16643,7 +16646,7 @@
         <v>884</v>
       </c>
       <c r="E203" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F203">
         <v>87.2</v>
@@ -16705,7 +16708,7 @@
         <v>885</v>
       </c>
       <c r="E204" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -16767,7 +16770,7 @@
         <v>886</v>
       </c>
       <c r="E205" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F205">
         <v>60.6</v>
@@ -16829,7 +16832,7 @@
         <v>887</v>
       </c>
       <c r="E206" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F206">
         <v>92</v>
@@ -16891,7 +16894,7 @@
         <v>888</v>
       </c>
       <c r="E207" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F207">
         <v>51.7</v>
@@ -16953,7 +16956,7 @@
         <v>889</v>
       </c>
       <c r="E208" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F208">
         <v>32.2</v>
@@ -17015,7 +17018,7 @@
         <v>890</v>
       </c>
       <c r="E209" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F209">
         <v>23.6</v>
@@ -17077,7 +17080,7 @@
         <v>891</v>
       </c>
       <c r="E210" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F210">
         <v>5425.5</v>
@@ -17139,7 +17142,7 @@
         <v>892</v>
       </c>
       <c r="E211" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F211">
         <v>544.9</v>
@@ -17201,7 +17204,7 @@
         <v>893</v>
       </c>
       <c r="E212" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F212">
         <v>761.9</v>
@@ -17263,7 +17266,7 @@
         <v>894</v>
       </c>
       <c r="E213" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F213">
         <v>493.8</v>
@@ -17325,7 +17328,7 @@
         <v>895</v>
       </c>
       <c r="E214" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F214">
         <v>291.3</v>
@@ -17387,7 +17390,7 @@
         <v>896</v>
       </c>
       <c r="E215" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F215">
         <v>476.1</v>
@@ -17449,7 +17452,7 @@
         <v>897</v>
       </c>
       <c r="E216" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F216">
         <v>677</v>
@@ -17511,7 +17514,7 @@
         <v>898</v>
       </c>
       <c r="E217" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F217">
         <v>221.3</v>
@@ -17573,7 +17576,7 @@
         <v>899</v>
       </c>
       <c r="E218" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F218">
         <v>342.2</v>
@@ -17635,7 +17638,7 @@
         <v>900</v>
       </c>
       <c r="E219" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F219">
         <v>251.1</v>
@@ -17697,7 +17700,7 @@
         <v>901</v>
       </c>
       <c r="E220" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F220">
         <v>425.8</v>
@@ -17759,7 +17762,7 @@
         <v>902</v>
       </c>
       <c r="E221" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -17821,7 +17824,7 @@
         <v>903</v>
       </c>
       <c r="E222" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F222">
         <v>877.5</v>
@@ -17881,444 +17884,444 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D3" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B4" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B5" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D5" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E5" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G5" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H5" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C6" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D6" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F6" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G6" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H6" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B7" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D7" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G7" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B8" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C8" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E8" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F8" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G8" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H8" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B9" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C9" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D9" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D10" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E10" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G10" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H10" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B11" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D11" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E11" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G11" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H11" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B12" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C12" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D12" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E12" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F12" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G12" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H12" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B13" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C13" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D13" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E13" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F13" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G13" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H13" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B14" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C14" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D14" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E14" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G14" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H14" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B15" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C15" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D15" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E15" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F15" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="G15" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H15" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B16" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C16" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D16" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E16" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="F16" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H16" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B17" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C17" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D17" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E17" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F17" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="G17" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H17" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
   </sheetData>
